--- a/Forex/analysis docs/Profitability analysis.xlsx
+++ b/Forex/analysis docs/Profitability analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eli_s\Documents\GitHub\Project S V6\Forex\analysis docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eli_s\Documents\GitHub\HiLo-DEV\Forex\analysis docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C7E243-A751-4FBC-81B4-48F06CD47BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35065259-FA1D-4A59-89CD-86DD4D71DC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="2988" windowWidth="23364" windowHeight="12108" xr2:uid="{DEB4A310-FF9A-4375-AF38-0D4AFE46D999}"/>
+    <workbookView xWindow="9804" yWindow="2076" windowWidth="26280" windowHeight="12108" xr2:uid="{DEB4A310-FF9A-4375-AF38-0D4AFE46D999}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="16">
   <si>
     <t>Spread</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>#Intervals</t>
+  </si>
+  <si>
+    <t>Silver</t>
   </si>
 </sst>
 </file>
@@ -432,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9219DD90-C32A-41C2-9F03-D699F505B50F}">
-  <dimension ref="B1:AN39"/>
+  <dimension ref="B1:BI39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -502,8 +505,11 @@
       <c r="AN1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AR1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1.2E-4</v>
       </c>
@@ -582,8 +588,41 @@
         <f>AL2/AF2</f>
         <v>-3.0000000000000037E-2</v>
       </c>
-    </row>
-    <row r="3" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AR2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>6</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1.2E-4</v>
       </c>
@@ -662,8 +701,47 @@
         <f t="shared" ref="AN3:AN4" si="11">AL3/AF3</f>
         <v>-1.0000000000000035E-2</v>
       </c>
-    </row>
-    <row r="4" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="AR3">
+        <v>3.8000000000000002E-4</v>
+      </c>
+      <c r="AS3">
+        <v>1.8E-3</v>
+      </c>
+      <c r="AV3">
+        <f>AS3-AR3</f>
+        <v>1.4199999999999998E-3</v>
+      </c>
+      <c r="AX3">
+        <f>AS3+AR3</f>
+        <v>2.1800000000000001E-3</v>
+      </c>
+      <c r="AZ3">
+        <v>1000</v>
+      </c>
+      <c r="BA3">
+        <v>100</v>
+      </c>
+      <c r="BB3">
+        <v>0.61</v>
+      </c>
+      <c r="BD3">
+        <f>BA3*AZ3 *(BB3*AV3)</f>
+        <v>86.61999999999999</v>
+      </c>
+      <c r="BE3">
+        <f>(BA3*AZ3* (1-BB3) *AX3)</f>
+        <v>85.02000000000001</v>
+      </c>
+      <c r="BG3">
+        <f>BD3-BE3</f>
+        <v>1.5999999999999801</v>
+      </c>
+      <c r="BI3">
+        <f>BG3/BA3</f>
+        <v>1.5999999999999803E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1.2E-4</v>
       </c>
@@ -743,7 +821,7 @@
         <v>9.9999999999999291E-3</v>
       </c>
     </row>
-    <row r="6" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1.2E-4</v>
       </c>
@@ -823,7 +901,7 @@
         <v>-2.0000000000000035E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1.2E-4</v>
       </c>
@@ -903,7 +981,7 @@
         <v>1.9999999999999931E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>1.2E-4</v>
       </c>
@@ -983,7 +1061,7 @@
         <v>2.3999999999999987E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1.2E-4</v>
       </c>
@@ -1020,7 +1098,7 @@
         <v>9.0000000000000036</v>
       </c>
     </row>
-    <row r="10" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:61" x14ac:dyDescent="0.3">
       <c r="S10">
         <f>Q6/K6</f>
         <v>0</v>
@@ -1065,7 +1143,7 @@
         <v>-2.5999999999999943E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>1.2E-4</v>
       </c>
@@ -1145,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>1.2E-4</v>
       </c>
@@ -1225,7 +1303,7 @@
         <v>2.5999999999999943E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1.2E-4</v>
       </c>
@@ -1305,7 +1383,7 @@
         <v>5.1999999999999956E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>1.2E-4</v>
       </c>
@@ -1342,7 +1420,7 @@
         <v>9.600000000000005</v>
       </c>
     </row>
-    <row r="15" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>1.2E-4</v>
       </c>
@@ -1383,7 +1461,7 @@
         <v>-1.1999999999999976E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:61" x14ac:dyDescent="0.3">
       <c r="S16">
         <f>Q12/K12</f>
         <v>2.4000000000000056E-2</v>

--- a/Forex/analysis docs/Profitability analysis.xlsx
+++ b/Forex/analysis docs/Profitability analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eli_s\Documents\GitHub\HiLo-DEV\Forex\analysis docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35065259-FA1D-4A59-89CD-86DD4D71DC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1938B03-D718-4EDE-A0CA-587C5E21FFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9804" yWindow="2076" windowWidth="26280" windowHeight="12108" xr2:uid="{DEB4A310-FF9A-4375-AF38-0D4AFE46D999}"/>
+    <workbookView xWindow="7476" yWindow="3144" windowWidth="26280" windowHeight="12108" xr2:uid="{DEB4A310-FF9A-4375-AF38-0D4AFE46D999}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="17">
   <si>
     <t>Spread</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Silver</t>
+  </si>
+  <si>
+    <t>Gold</t>
   </si>
 </sst>
 </file>
@@ -820,6 +823,45 @@
         <f t="shared" si="11"/>
         <v>9.9999999999999291E-3</v>
       </c>
+      <c r="AR4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="AS4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="AV4">
+        <f>AS4-AR4</f>
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="AX4">
+        <f>AS4+AR4</f>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="AZ4">
+        <v>1000</v>
+      </c>
+      <c r="BA4">
+        <v>100</v>
+      </c>
+      <c r="BB4">
+        <v>0.67</v>
+      </c>
+      <c r="BD4">
+        <f>BA4*AZ4 *(BB4*AV4)</f>
+        <v>60.300000000000004</v>
+      </c>
+      <c r="BE4">
+        <f>(BA4*AZ4* (1-BB4) *AX4)</f>
+        <v>89.09999999999998</v>
+      </c>
+      <c r="BG4">
+        <f>BD4-BE4</f>
+        <v>-28.799999999999976</v>
+      </c>
+      <c r="BI4">
+        <f>BG4/BA4</f>
+        <v>-0.28799999999999976</v>
+      </c>
     </row>
     <row r="6" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B6">
@@ -1302,6 +1344,9 @@
         <f t="shared" si="34"/>
         <v>2.5999999999999943E-2</v>
       </c>
+      <c r="AR12" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B13">
@@ -1382,6 +1427,39 @@
         <f t="shared" si="34"/>
         <v>5.1999999999999956E-2</v>
       </c>
+      <c r="AR13" t="s">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>3</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>6</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B14">
@@ -1419,6 +1497,45 @@
         <f t="shared" si="44"/>
         <v>9.600000000000005</v>
       </c>
+      <c r="AR14">
+        <v>1.2999999999999999E-4</v>
+      </c>
+      <c r="AS14">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="AV14">
+        <f>AS14-AR14</f>
+        <v>7.6999999999999996E-4</v>
+      </c>
+      <c r="AX14">
+        <f>AS14+AR14</f>
+        <v>1.0299999999999999E-3</v>
+      </c>
+      <c r="AZ14">
+        <v>1000</v>
+      </c>
+      <c r="BA14">
+        <v>100</v>
+      </c>
+      <c r="BB14">
+        <v>0.6</v>
+      </c>
+      <c r="BD14">
+        <f>BA14*AZ14 *(BB14*AV14)</f>
+        <v>46.199999999999996</v>
+      </c>
+      <c r="BE14">
+        <f>(BA14*AZ14* (1-BB14) *AX14)</f>
+        <v>41.199999999999996</v>
+      </c>
+      <c r="BG14">
+        <f>BD14-BE14</f>
+        <v>5</v>
+      </c>
+      <c r="BI14">
+        <f>BG14/BA14</f>
+        <v>0.05</v>
+      </c>
     </row>
     <row r="15" spans="2:61" x14ac:dyDescent="0.3">
       <c r="B15">
@@ -1459,6 +1576,45 @@
       <c r="S15">
         <f>Q11/K11</f>
         <v>-1.1999999999999976E-2</v>
+      </c>
+      <c r="AR15">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="AS15">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="AV15">
+        <f>AS15-AR15</f>
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="AX15">
+        <f>AS15+AR15</f>
+        <v>1.0499999999999999E-3</v>
+      </c>
+      <c r="AZ15">
+        <v>1000</v>
+      </c>
+      <c r="BA15">
+        <v>100</v>
+      </c>
+      <c r="BB15">
+        <v>0.6</v>
+      </c>
+      <c r="BD15">
+        <f>BA15*AZ15 *(BB15*AV15)</f>
+        <v>45</v>
+      </c>
+      <c r="BE15">
+        <f>(BA15*AZ15* (1-BB15) *AX15)</f>
+        <v>42</v>
+      </c>
+      <c r="BG15">
+        <f>BD15-BE15</f>
+        <v>3</v>
+      </c>
+      <c r="BI15">
+        <f>BG15/BA15</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="2:61" x14ac:dyDescent="0.3">

--- a/Forex/analysis docs/Profitability analysis.xlsx
+++ b/Forex/analysis docs/Profitability analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eli_s\Documents\GitHub\HiLo-DEV\Forex\analysis docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1938B03-D718-4EDE-A0CA-587C5E21FFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F97A20D-257C-4EBC-8186-114394B70930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7476" yWindow="3144" windowWidth="26280" windowHeight="12108" xr2:uid="{DEB4A310-FF9A-4375-AF38-0D4AFE46D999}"/>
+    <workbookView xWindow="-96" yWindow="4488" windowWidth="30960" windowHeight="12168" xr2:uid="{DEB4A310-FF9A-4375-AF38-0D4AFE46D999}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1661,6 +1661,45 @@
         <f t="shared" ref="AN16:AN19" si="50">AL16/AF16</f>
         <v>-9.9999999999999638E-3</v>
       </c>
+      <c r="AR16">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="AS16">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="AV16">
+        <f>AS16-AR16</f>
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="AX16">
+        <f>AS16+AR16</f>
+        <v>1.0499999999999999E-3</v>
+      </c>
+      <c r="AZ16">
+        <v>1000</v>
+      </c>
+      <c r="BA16">
+        <v>100</v>
+      </c>
+      <c r="BB16">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="BD16">
+        <f>BA16*AZ16 *(BB16*AV16)</f>
+        <v>44.1</v>
+      </c>
+      <c r="BE16">
+        <f>(BA16*AZ16* (1-BB16) *AX16)</f>
+        <v>43.26</v>
+      </c>
+      <c r="BG16">
+        <f>BD16-BE16</f>
+        <v>0.84000000000000341</v>
+      </c>
+      <c r="BI16">
+        <f>BG16/BA16</f>
+        <v>8.4000000000000342E-3</v>
+      </c>
     </row>
     <row r="17" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B17">
